--- a/Result/profitability/2613.xlsx
+++ b/Result/profitability/2613.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.28</v>
+        <v>0.2975</v>
       </c>
       <c r="N2" t="n">
-        <v>16.7425</v>
+        <v>16.74</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32125</v>
+        <v>0.385</v>
       </c>
       <c r="N3" t="n">
-        <v>16.8675</v>
+        <v>16.96375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4025</v>
+        <v>0.43625</v>
       </c>
       <c r="N4" t="n">
-        <v>16.655</v>
+        <v>17.05125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5125</v>
+        <v>0.5425</v>
       </c>
       <c r="N5" t="n">
-        <v>16.56</v>
+        <v>16.55625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45125</v>
+        <v>0.4687499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.41125</v>
+        <v>14.3875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26375</v>
+        <v>0.29</v>
       </c>
       <c r="N7" t="n">
-        <v>11.2125</v>
+        <v>11.41375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.205</v>
+        <v>0.245</v>
       </c>
       <c r="N8" t="n">
-        <v>9.54125</v>
+        <v>10.11375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2613</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>917</v>
+      </c>
+      <c r="D75" t="n">
+        <v>752</v>
+      </c>
+      <c r="E75" t="n">
+        <v>165</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>109</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.93%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>87</v>
+      </c>
+      <c r="K75" t="n">
+        <v>69</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.27125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.80375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.579999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3402674591381871</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9230769230769229</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.001660210293303876</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
